--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486686_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486686_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.0816</v>
+        <v>1.7795</v>
       </c>
       <c r="E2" t="n">
-        <v>1.7395</v>
+        <v>2.0085</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3421</v>
+        <v>-0.229</v>
       </c>
       <c r="G2" t="n">
         <v>-1.5577</v>
@@ -610,13 +610,13 @@
         <v>2.3169</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.5457</v>
+        <v>-0.8479</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.497</v>
+        <v>-0.228</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0487</v>
+        <v>-0.6198</v>
       </c>
       <c r="V2" t="n">
         <v>3.0266</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.1064</v>
+        <v>-0.0235</v>
       </c>
       <c r="E3" t="n">
-        <v>3.2946</v>
+        <v>3.2533</v>
       </c>
       <c r="F3" t="n">
-        <v>-3.401</v>
+        <v>-3.2768</v>
       </c>
       <c r="G3" t="n">
         <v>0.08699999999999999</v>
@@ -688,13 +688,13 @@
         <v>1.7377</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.0003</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4684</v>
+        <v>0.4271</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4687</v>
+        <v>-0.3445</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. GONZALEZ GRANDE</t>
+          <t>A. DELGADO LUIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.6086</v>
+        <v>-1.1318</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8253</v>
+        <v>-1.0489</v>
       </c>
       <c r="F4" t="n">
-        <v>-3.4339</v>
+        <v>-0.0829</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.129</v>
+        <v>-0.0423</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.3377</v>
+        <v>0.3172</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7913</v>
+        <v>-0.3595</v>
       </c>
       <c r="J4" t="n">
-        <v>0.3888</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.303</v>
+        <v>0.0414</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6918</v>
+        <v>0.0407</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.5178</v>
+        <v>-0.1244</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.0348</v>
+        <v>0.2758</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.483</v>
+        <v>-0.4002</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1585</v>
+        <v>-0.7723</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1585</v>
+        <v>0.1931</v>
       </c>
       <c r="S4" t="n">
-        <v>1.8752</v>
+        <v>-0.3172</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1509</v>
+        <v>-0.1655</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.2757</v>
+        <v>-0.1516</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.5133</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.7989</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. DELGADO LUIS</t>
+          <t>P. GRIMA LORENZO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.2063</v>
+        <v>-1.2908</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.0489</v>
+        <v>-0.9313</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.1574</v>
+        <v>-0.3596</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.0423</v>
+        <v>1.5296</v>
       </c>
       <c r="H5" t="n">
-        <v>0.3172</v>
+        <v>0.9373</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.3595</v>
+        <v>0.5923</v>
       </c>
       <c r="J5" t="n">
-        <v>0.08210000000000001</v>
+        <v>0.5516</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0414</v>
+        <v>1.076</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0407</v>
+        <v>-0.5244</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1244</v>
+        <v>0.978</v>
       </c>
       <c r="N5" t="n">
-        <v>0.2758</v>
+        <v>-0.1387</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.4002</v>
+        <v>1.1167</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.7723</v>
+        <v>-0.1931</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9654</v>
+        <v>-1.1585</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1931</v>
+        <v>0.9654</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.3917</v>
+        <v>-1.3997</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.1655</v>
+        <v>-0.3244</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2261</v>
+        <v>-1.0753</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.2277</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. GRIMA LORENZO</t>
+          <t>R. GONZALEZ GRANDE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.9984</v>
+        <v>-1.8496</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2416</v>
+        <v>1.5843</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.7569</v>
+        <v>-3.4339</v>
       </c>
       <c r="G6" t="n">
-        <v>1.5296</v>
+        <v>-2.129</v>
       </c>
       <c r="H6" t="n">
-        <v>0.9373</v>
+        <v>-1.3377</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5923</v>
+        <v>-0.7913</v>
       </c>
       <c r="J6" t="n">
-        <v>0.5516</v>
+        <v>0.3888</v>
       </c>
       <c r="K6" t="n">
-        <v>1.076</v>
+        <v>-0.303</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.5244</v>
+        <v>0.6918</v>
       </c>
       <c r="M6" t="n">
-        <v>0.978</v>
+        <v>-2.5178</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1387</v>
+        <v>-1.0348</v>
       </c>
       <c r="O6" t="n">
-        <v>1.1167</v>
+        <v>-1.483</v>
       </c>
       <c r="P6" t="n">
-        <v>-0.1931</v>
+        <v>1.1585</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1585</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9654</v>
+        <v>1.1585</v>
       </c>
       <c r="S6" t="n">
-        <v>-2.1072</v>
+        <v>0.6342</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6347</v>
+        <v>0.9099</v>
       </c>
       <c r="U6" t="n">
-        <v>-1.4726</v>
+        <v>-0.2757</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2277</v>
+        <v>-1.5133</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.2856</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.2277</v>
+        <v>-1.7989</v>
       </c>
     </row>
     <row r="7">
@@ -955,10 +955,10 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.7868</v>
+        <v>-2.6282</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5034999999999999</v>
+        <v>-0.3449</v>
       </c>
       <c r="F7" t="n">
         <v>-2.2833</v>
@@ -1000,10 +1000,10 @@
         <v>0.7723</v>
       </c>
       <c r="S7" t="n">
-        <v>0.08260000000000001</v>
+        <v>0.2412</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0825</v>
+        <v>0.2411</v>
       </c>
       <c r="U7" t="n">
         <v>0.0001</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-3.8239</v>
+        <v>-3.3247</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5457</v>
+        <v>-1.0217</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.2782</v>
+        <v>-2.303</v>
       </c>
       <c r="G8" t="n">
         <v>-3.5671</v>
@@ -1078,13 +1078,13 @@
         <v>1.3515</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.0371</v>
+        <v>-0.5379</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8829</v>
+        <v>-0.3589</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1542</v>
+        <v>-0.179</v>
       </c>
       <c r="V8" t="n">
         <v>-0.5712</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-4.265</v>
+        <v>-3.5975</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.5411</v>
+        <v>-2.0722</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.724</v>
+        <v>-1.5253</v>
       </c>
       <c r="G9" t="n">
         <v>1.035</v>
@@ -1156,13 +1156,13 @@
         <v>1.5446</v>
       </c>
       <c r="S9" t="n">
-        <v>-2.1568</v>
+        <v>-1.4893</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.9657</v>
+        <v>-0.4969</v>
       </c>
       <c r="U9" t="n">
-        <v>-1.1911</v>
+        <v>-0.9923999999999999</v>
       </c>
       <c r="V9" t="n">
         <v>-1.5985</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.338</v>
+        <v>-3.6483</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.007</v>
+        <v>-1.6898</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.331</v>
+        <v>-1.9585</v>
       </c>
       <c r="G10" t="n">
         <v>-0.0252</v>
@@ -1234,13 +1234,13 @@
         <v>1.5446</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.5172</v>
+        <v>-0.8275</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3038</v>
+        <v>0.0134</v>
       </c>
       <c r="U10" t="n">
-        <v>-1.2134</v>
+        <v>-0.8409</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2856</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.0585</v>
+        <v>-6.5676</v>
       </c>
       <c r="E11" t="n">
-        <v>-5.4531</v>
+        <v>-5.391</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6054</v>
+        <v>-1.1766</v>
       </c>
       <c r="G11" t="n">
         <v>-3.9309</v>
@@ -1312,13 +1312,13 @@
         <v>1.9308</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.6836</v>
+        <v>-1.1926</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.497</v>
+        <v>-0.4349</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1866</v>
+        <v>-0.7577</v>
       </c>
       <c r="V11" t="n">
         <v>-0.2856</v>
@@ -1345,19 +1345,19 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-23.1103</v>
+        <v>-22.2825</v>
       </c>
       <c r="E12" t="n">
-        <v>-6.4815</v>
+        <v>-5.6537</v>
       </c>
       <c r="F12" t="n">
-        <v>-16.629</v>
+        <v>-16.6289</v>
       </c>
       <c r="G12" t="n">
         <v>-12.2423</v>
       </c>
       <c r="H12" t="n">
-        <v>-4.1376</v>
+        <v>-4.137599999999999</v>
       </c>
       <c r="I12" t="n">
         <v>-8.1046</v>
@@ -1390,13 +1390,13 @@
         <v>13.5154</v>
       </c>
       <c r="S12" t="n">
-        <v>-6.481800000000001</v>
+        <v>-5.6541</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.2448</v>
+        <v>-0.4171</v>
       </c>
       <c r="U12" t="n">
-        <v>-5.237</v>
+        <v>-5.2368</v>
       </c>
       <c r="V12" t="n">
         <v>-2.4553</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>9.0443</v>
+        <v>9.5214</v>
       </c>
       <c r="E13" t="n">
-        <v>7.7911</v>
+        <v>8.204800000000001</v>
       </c>
       <c r="F13" t="n">
-        <v>1.2532</v>
+        <v>1.3166</v>
       </c>
       <c r="G13" t="n">
         <v>8.569599999999999</v>
@@ -1468,13 +1468,13 @@
         <v>0.9654</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.4906</v>
+        <v>-0.0136</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.2759</v>
+        <v>0.1378</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.2147</v>
+        <v>-0.1513</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>A. TRAORE</t>
+          <t>V. NEGRE FABREGAT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.168</v>
+        <v>4.8274</v>
       </c>
       <c r="E14" t="n">
-        <v>6.2488</v>
+        <v>2.3166</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.0808</v>
+        <v>2.5109</v>
       </c>
       <c r="G14" t="n">
-        <v>1.4942</v>
+        <v>3.9846</v>
       </c>
       <c r="H14" t="n">
-        <v>2.2968</v>
+        <v>-0.1796</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8026</v>
+        <v>4.1642</v>
       </c>
       <c r="J14" t="n">
-        <v>3.3848</v>
+        <v>3.0684</v>
       </c>
       <c r="K14" t="n">
-        <v>3.2627</v>
+        <v>-0.5239</v>
       </c>
       <c r="L14" t="n">
-        <v>0.1221</v>
+        <v>3.5924</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.8906</v>
+        <v>0.9162</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.9659</v>
+        <v>0.3443</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.9247</v>
+        <v>0.5719</v>
       </c>
       <c r="P14" t="n">
-        <v>-1.3515</v>
+        <v>0.3862</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.8962</v>
+        <v>-0.9654</v>
       </c>
       <c r="R14" t="n">
-        <v>1.5446</v>
+        <v>1.3515</v>
       </c>
       <c r="S14" t="n">
-        <v>4.5121</v>
+        <v>-0.1998</v>
       </c>
       <c r="T14" t="n">
-        <v>4.2469</v>
+        <v>0.2135</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2652</v>
+        <v>-0.4134</v>
       </c>
       <c r="V14" t="n">
-        <v>1.5133</v>
+        <v>0.6565</v>
       </c>
       <c r="W14" t="n">
-        <v>1.5133</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>0.6565</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>V. NEGRE FABREGAT</t>
+          <t>G. PEREZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.9627</v>
+        <v>4.3762</v>
       </c>
       <c r="E15" t="n">
-        <v>1.7995</v>
+        <v>2.4253</v>
       </c>
       <c r="F15" t="n">
-        <v>2.1632</v>
+        <v>1.951</v>
       </c>
       <c r="G15" t="n">
-        <v>3.9846</v>
+        <v>4.2588</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.1796</v>
+        <v>2.4548</v>
       </c>
       <c r="I15" t="n">
-        <v>4.1642</v>
+        <v>1.804</v>
       </c>
       <c r="J15" t="n">
-        <v>3.0684</v>
+        <v>3.2047</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.5239</v>
+        <v>1.6968</v>
       </c>
       <c r="L15" t="n">
-        <v>3.5924</v>
+        <v>1.5079</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9162</v>
+        <v>1.0541</v>
       </c>
       <c r="N15" t="n">
-        <v>0.3443</v>
+        <v>0.758</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5719</v>
+        <v>0.2961</v>
       </c>
       <c r="P15" t="n">
-        <v>0.3862</v>
+        <v>0.1931</v>
       </c>
       <c r="Q15" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3515</v>
+        <v>1.1585</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0646</v>
+        <v>-0.0756</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.3036</v>
+        <v>0.186</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.761</v>
+        <v>-0.2616</v>
       </c>
       <c r="V15" t="n">
-        <v>0.6565</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.6565</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.935</v>
+        <v>3.819</v>
       </c>
       <c r="E16" t="n">
-        <v>1.0269</v>
+        <v>1.2337</v>
       </c>
       <c r="F16" t="n">
-        <v>2.9081</v>
+        <v>2.5853</v>
       </c>
       <c r="G16" t="n">
         <v>2.3154</v>
@@ -1702,13 +1702,13 @@
         <v>1.7377</v>
       </c>
       <c r="S16" t="n">
-        <v>0.585</v>
+        <v>0.469</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.08309999999999999</v>
+        <v>0.1238</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6681</v>
+        <v>0.3452</v>
       </c>
       <c r="V16" t="n">
         <v>1.2277</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>G. PEREZ HERNANDEZ</t>
+          <t>A. TRAORE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,64 +1735,64 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.6467</v>
+        <v>3.4624</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9082</v>
+        <v>3.7667</v>
       </c>
       <c r="F17" t="n">
-        <v>1.7386</v>
+        <v>-0.3043</v>
       </c>
       <c r="G17" t="n">
-        <v>4.2588</v>
+        <v>1.4942</v>
       </c>
       <c r="H17" t="n">
-        <v>2.4548</v>
+        <v>2.2968</v>
       </c>
       <c r="I17" t="n">
-        <v>1.804</v>
+        <v>-0.8026</v>
       </c>
       <c r="J17" t="n">
-        <v>3.2047</v>
+        <v>3.3848</v>
       </c>
       <c r="K17" t="n">
-        <v>1.6968</v>
+        <v>3.2627</v>
       </c>
       <c r="L17" t="n">
-        <v>1.5079</v>
+        <v>0.1221</v>
       </c>
       <c r="M17" t="n">
-        <v>1.0541</v>
+        <v>-1.8906</v>
       </c>
       <c r="N17" t="n">
-        <v>0.758</v>
+        <v>-0.9659</v>
       </c>
       <c r="O17" t="n">
-        <v>0.2961</v>
+        <v>-0.9247</v>
       </c>
       <c r="P17" t="n">
-        <v>0.1931</v>
+        <v>-1.3515</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9654</v>
+        <v>-2.8962</v>
       </c>
       <c r="R17" t="n">
-        <v>1.1585</v>
+        <v>1.5446</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8051</v>
+        <v>1.8064</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3311</v>
+        <v>1.7648</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.474</v>
+        <v>0.0417</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>1.5133</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>1.5133</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.5287</v>
+        <v>0.9426</v>
       </c>
       <c r="E18" t="n">
-        <v>4.1917</v>
+        <v>3.4678</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.663</v>
+        <v>-2.5251</v>
       </c>
       <c r="G18" t="n">
         <v>-0.08450000000000001</v>
@@ -1858,13 +1858,13 @@
         <v>1.1585</v>
       </c>
       <c r="S18" t="n">
-        <v>1.6824</v>
+        <v>1.0963</v>
       </c>
       <c r="T18" t="n">
-        <v>1.7097</v>
+        <v>0.9857</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0273</v>
+        <v>0.1106</v>
       </c>
       <c r="V18" t="n">
         <v>-1.2277</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6717</v>
+        <v>0.9034</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0315</v>
+        <v>1.2383</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.3598</v>
+        <v>-0.3349</v>
       </c>
       <c r="G19" t="n">
         <v>-0.0244</v>
@@ -1936,13 +1936,13 @@
         <v>1.9308</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9817</v>
+        <v>1.2134</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4132</v>
+        <v>0.6201</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5685</v>
+        <v>0.5933</v>
       </c>
       <c r="V19" t="n">
         <v>-0.2856</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0987</v>
+        <v>0.8971</v>
       </c>
       <c r="E20" t="n">
-        <v>1.2363</v>
+        <v>1.9602</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.1376</v>
+        <v>-1.0631</v>
       </c>
       <c r="G20" t="n">
         <v>-1.7161</v>
@@ -2014,13 +2014,13 @@
         <v>1.9308</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.116</v>
+        <v>0.6824</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.1659</v>
+        <v>0.5581</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0499</v>
+        <v>0.1244</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. AMON BYSTROVA</t>
+          <t>J. SCHILB</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.002</v>
+        <v>-0.3119</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.3692</v>
+        <v>0.585</v>
       </c>
       <c r="F21" t="n">
-        <v>2.3672</v>
+        <v>-0.8969</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9525</v>
+        <v>-0.6428</v>
       </c>
       <c r="H21" t="n">
-        <v>-1.1513</v>
+        <v>-1.5448</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1989</v>
+        <v>0.902</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.3237</v>
+        <v>0.6541</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.7713</v>
+        <v>-0.6481</v>
       </c>
       <c r="L21" t="n">
-        <v>0.4476</v>
+        <v>1.3022</v>
       </c>
       <c r="M21" t="n">
-        <v>0.3713</v>
+        <v>-1.2969</v>
       </c>
       <c r="N21" t="n">
-        <v>0.62</v>
+        <v>-0.8967000000000001</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2487</v>
+        <v>-0.4002</v>
       </c>
       <c r="P21" t="n">
-        <v>0.5792</v>
+        <v>0.1931</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.5446</v>
+        <v>0.1931</v>
       </c>
       <c r="S21" t="n">
-        <v>1.0703</v>
+        <v>0.1379</v>
       </c>
       <c r="T21" t="n">
-        <v>0.6616</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>0.4087</v>
+        <v>0.2069</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6991000000000001</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.7417</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0.0426</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. SCHILB</t>
+          <t>A. AMON BYSTROVA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6429</v>
+        <v>-0.3275</v>
       </c>
       <c r="E22" t="n">
-        <v>0.3781</v>
+        <v>-2.7829</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.021</v>
+        <v>2.4554</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.6428</v>
+        <v>-0.9525</v>
       </c>
       <c r="H22" t="n">
-        <v>-1.5448</v>
+        <v>-1.1513</v>
       </c>
       <c r="I22" t="n">
-        <v>0.902</v>
+        <v>0.1989</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6541</v>
+        <v>-1.3237</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6481</v>
+        <v>-1.7713</v>
       </c>
       <c r="L22" t="n">
-        <v>1.3022</v>
+        <v>0.4476</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.2969</v>
+        <v>0.3713</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8967000000000001</v>
+        <v>0.62</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.4002</v>
+        <v>-0.2487</v>
       </c>
       <c r="P22" t="n">
-        <v>0.1931</v>
+        <v>0.5792</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R22" t="n">
-        <v>0.1931</v>
+        <v>1.5446</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1931</v>
+        <v>0.7448</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2759</v>
+        <v>0.2479</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0828</v>
+        <v>0.4969</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.6991000000000001</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-0.7417</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.0426</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.3007</v>
+        <v>-4.3106</v>
       </c>
       <c r="E23" t="n">
-        <v>-6.614</v>
+        <v>-5.7866</v>
       </c>
       <c r="F23" t="n">
-        <v>1.3133</v>
+        <v>1.476</v>
       </c>
       <c r="G23" t="n">
         <v>-4.9601</v>
@@ -2248,13 +2248,13 @@
         <v>1.9308</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3199</v>
+        <v>1.31</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.359</v>
+        <v>0.4684</v>
       </c>
       <c r="U23" t="n">
-        <v>0.6788999999999999</v>
+        <v>0.8416</v>
       </c>
       <c r="V23" t="n">
         <v>1.2703</v>
@@ -2281,19 +2281,19 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>23.1102</v>
+        <v>23.7995</v>
       </c>
       <c r="E24" t="n">
         <v>16.6289</v>
       </c>
       <c r="F24" t="n">
-        <v>6.481400000000001</v>
+        <v>7.1709</v>
       </c>
       <c r="G24" t="n">
-        <v>12.24219999999999</v>
+        <v>12.2422</v>
       </c>
       <c r="H24" t="n">
-        <v>4.1376</v>
+        <v>4.137600000000001</v>
       </c>
       <c r="I24" t="n">
         <v>8.104599999999998</v>
@@ -2302,7 +2302,7 @@
         <v>19.8388</v>
       </c>
       <c r="K24" t="n">
-        <v>5.8673</v>
+        <v>5.867299999999999</v>
       </c>
       <c r="L24" t="n">
         <v>13.9717</v>
@@ -2326,13 +2326,13 @@
         <v>15.4463</v>
       </c>
       <c r="S24" t="n">
-        <v>6.481999999999999</v>
+        <v>7.171200000000001</v>
       </c>
       <c r="T24" t="n">
-        <v>5.2369</v>
+        <v>5.236999999999999</v>
       </c>
       <c r="U24" t="n">
-        <v>1.2451</v>
+        <v>1.9343</v>
       </c>
       <c r="V24" t="n">
         <v>2.4554</v>
